--- a/VerveStacks_IND_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D28FAF8-ED57-46AC-B0C3-FA82FFEE8208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD305CEC-55CB-4FA1-8738-96C10C90E81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4374" uniqueCount="1245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4376" uniqueCount="1246">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -3863,6 +3863,9 @@
   </si>
   <si>
     <t>e_w116541259-400_IND</t>
+  </si>
+  <si>
+    <t>start</t>
   </si>
 </sst>
 </file>
@@ -21057,7 +21060,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23C81388-D103-4954-9025-DC479EDEBA7C}">
-  <dimension ref="B9:S128"/>
+  <dimension ref="B9:S129"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:19">
@@ -24550,6 +24553,17 @@
       </c>
       <c r="K128" t="s">
         <v>1193</v>
+      </c>
+    </row>
+    <row r="129" spans="2:11">
+      <c r="B129" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E129">
+        <v>2100</v>
+      </c>
+      <c r="K129" t="s">
+        <v>1245</v>
       </c>
     </row>
   </sheetData>
